--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131082792</v>
+        <v>131082791</v>
       </c>
       <c r="B2" t="n">
         <v>79244</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459715</v>
+        <v>459785</v>
       </c>
       <c r="R2" t="n">
-        <v>7046426</v>
+        <v>7046451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131082791</v>
+        <v>131082792</v>
       </c>
       <c r="B3" t="n">
         <v>79244</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459785</v>
+        <v>459715</v>
       </c>
       <c r="R3" t="n">
-        <v>7046451</v>
+        <v>7046426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131082791</v>
+        <v>131082792</v>
       </c>
       <c r="B2" t="n">
         <v>79244</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459785</v>
+        <v>459715</v>
       </c>
       <c r="R2" t="n">
-        <v>7046451</v>
+        <v>7046426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131082792</v>
+        <v>131082791</v>
       </c>
       <c r="B3" t="n">
         <v>79244</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459715</v>
+        <v>459785</v>
       </c>
       <c r="R3" t="n">
-        <v>7046426</v>
+        <v>7046451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082792</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131082791</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131082790</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131082789</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082792</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131082791</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131082790</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131082789</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082792</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131082791</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131082790</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131082789</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>131082782</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131082784</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>131082781</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082780</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131082783</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082792</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131082791</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131082790</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131082789</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>131082782</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131082784</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>131082781</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082780</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131082783</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082792</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131082791</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131082790</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131082789</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>131082782</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131082784</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>131082781</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082780</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131082783</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -1491,7 +1491,7 @@
         <v>131082780</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131082783</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -1491,7 +1491,7 @@
         <v>131082780</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131082783</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131082792</v>
+        <v>131082789</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459715</v>
+        <v>459958</v>
       </c>
       <c r="R2" t="n">
-        <v>7046426</v>
+        <v>7046508</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,14 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131082791</v>
+        <v>131082790</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459785</v>
+        <v>459913</v>
       </c>
       <c r="R3" t="n">
-        <v>7046451</v>
+        <v>7046493</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera stående döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,14 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131082790</v>
+        <v>131082791</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459913</v>
+        <v>459785</v>
       </c>
       <c r="R4" t="n">
-        <v>7046493</v>
+        <v>7046451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera stående döda granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,14 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131082789</v>
+        <v>131082792</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459958</v>
+        <v>459715</v>
       </c>
       <c r="R5" t="n">
-        <v>7046508</v>
+        <v>7046426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131082782</v>
+        <v>131082778</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459863</v>
+        <v>459982</v>
       </c>
       <c r="R6" t="n">
-        <v>7046470</v>
+        <v>7046511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131082784</v>
+        <v>131082779</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459807</v>
+        <v>459964</v>
       </c>
       <c r="R7" t="n">
-        <v>7046453</v>
+        <v>7046508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka på en gran vid en hyggeskant. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131082781</v>
+        <v>131082780</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459874</v>
+        <v>459925</v>
       </c>
       <c r="R8" t="n">
-        <v>7046477</v>
+        <v>7046501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en klen gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131082780</v>
+        <v>131082781</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459925</v>
+        <v>459874</v>
       </c>
       <c r="R9" t="n">
-        <v>7046501</v>
+        <v>7046477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, enstaka på en klen gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082783</v>
+        <v>131082782</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459823</v>
+        <v>459863</v>
       </c>
       <c r="R10" t="n">
-        <v>7046455</v>
+        <v>7046470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,6 +1755,276 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131082783</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hävlarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>459823</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7046455</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131082784</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hävlarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>459807</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7046453</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, enstaka på en gran vid en hyggeskant. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63852-2025 artfynd.xlsx
+++ b/artfynd/A 63852-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082790</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082778</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082779</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082780</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1620,6 +1660,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082781</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1755,6 +1800,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082782</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1890,6 +1940,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082783</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2025,8 +2080,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>